--- a/auth.xlsx
+++ b/auth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\preditiva\PREDITIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D2E2F31-6770-4114-8EC5-11C1EA4F289B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F212AB-D106-42F3-AEFC-FA363EB6E313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6A472DFD-0E09-42DB-874E-9233951C7FB7}"/>
   </bookViews>
@@ -33,12 +33,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Usuario</t>
   </si>
   <si>
     <t>Senha</t>
+  </si>
+  <si>
+    <t>admin</t>
   </si>
 </sst>
 </file>
@@ -426,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F37F4D-7674-4A32-8889-363E089154EA}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -445,8 +448,8 @@
         <v>11</v>
       </c>
       <c r="B2" t="str">
-        <f>A2 &amp; " - kidy@2025"</f>
-        <v>11 - kidy@2025</v>
+        <f>A2&amp;"kidy@2025"</f>
+        <v>11kidy@2025</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -454,8 +457,8 @@
         <v>15</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B52" si="0">A3 &amp; " - kidy@2025"</f>
-        <v>15 - kidy@2025</v>
+        <f t="shared" ref="B3:B52" si="0">A3&amp;"kidy@2025"</f>
+        <v>15kidy@2025</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -464,7 +467,7 @@
       </c>
       <c r="B4" t="str">
         <f t="shared" si="0"/>
-        <v>19 - kidy@2025</v>
+        <v>19kidy@2025</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -473,7 +476,7 @@
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
-        <v>23 - kidy@2025</v>
+        <v>23kidy@2025</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -482,7 +485,7 @@
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
-        <v>31 - kidy@2025</v>
+        <v>31kidy@2025</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -491,7 +494,7 @@
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
-        <v>34 - kidy@2025</v>
+        <v>34kidy@2025</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -500,7 +503,7 @@
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
-        <v>38 - kidy@2025</v>
+        <v>38kidy@2025</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -509,7 +512,7 @@
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
-        <v>39 - kidy@2025</v>
+        <v>39kidy@2025</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -518,7 +521,7 @@
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
-        <v>41 - kidy@2025</v>
+        <v>41kidy@2025</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -527,7 +530,7 @@
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
-        <v>45 - kidy@2025</v>
+        <v>45kidy@2025</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -536,7 +539,7 @@
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
-        <v>46 - kidy@2025</v>
+        <v>46kidy@2025</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -545,7 +548,7 @@
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
-        <v>53 - kidy@2025</v>
+        <v>53kidy@2025</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -554,7 +557,7 @@
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
-        <v>61 - kidy@2025</v>
+        <v>61kidy@2025</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -563,7 +566,7 @@
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
-        <v>65 - kidy@2025</v>
+        <v>65kidy@2025</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -572,7 +575,7 @@
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
-        <v>74 - kidy@2025</v>
+        <v>74kidy@2025</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -581,7 +584,7 @@
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
-        <v>93 - kidy@2025</v>
+        <v>93kidy@2025</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -590,7 +593,7 @@
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
-        <v>143 - kidy@2025</v>
+        <v>143kidy@2025</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -599,7 +602,7 @@
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
-        <v>167 - kidy@2025</v>
+        <v>167kidy@2025</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -608,7 +611,7 @@
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
-        <v>371 - kidy@2025</v>
+        <v>371kidy@2025</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -617,7 +620,7 @@
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
-        <v>178 - kidy@2025</v>
+        <v>178kidy@2025</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -626,7 +629,7 @@
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
-        <v>187 - kidy@2025</v>
+        <v>187kidy@2025</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -635,7 +638,7 @@
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
-        <v>194 - kidy@2025</v>
+        <v>194kidy@2025</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,7 +647,7 @@
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
-        <v>197 - kidy@2025</v>
+        <v>197kidy@2025</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -653,7 +656,7 @@
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
-        <v>208 - kidy@2025</v>
+        <v>208kidy@2025</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -662,7 +665,7 @@
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
-        <v>217 - kidy@2025</v>
+        <v>217kidy@2025</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -671,7 +674,7 @@
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
-        <v>218 - kidy@2025</v>
+        <v>218kidy@2025</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -680,7 +683,7 @@
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
-        <v>231 - kidy@2025</v>
+        <v>231kidy@2025</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -689,7 +692,7 @@
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
-        <v>232 - kidy@2025</v>
+        <v>232kidy@2025</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -698,7 +701,7 @@
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
-        <v>240 - kidy@2025</v>
+        <v>240kidy@2025</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -707,7 +710,7 @@
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
-        <v>248 - kidy@2025</v>
+        <v>248kidy@2025</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -716,7 +719,7 @@
       </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
-        <v>261 - kidy@2025</v>
+        <v>261kidy@2025</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -725,7 +728,7 @@
       </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
-        <v>266 - kidy@2025</v>
+        <v>266kidy@2025</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -734,7 +737,7 @@
       </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
-        <v>267 - kidy@2025</v>
+        <v>267kidy@2025</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -743,7 +746,7 @@
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
-        <v>270 - kidy@2025</v>
+        <v>270kidy@2025</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -752,7 +755,7 @@
       </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
-        <v>273 - kidy@2025</v>
+        <v>273kidy@2025</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -761,7 +764,7 @@
       </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
-        <v>282 - kidy@2025</v>
+        <v>282kidy@2025</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -770,7 +773,7 @@
       </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
-        <v>291 - kidy@2025</v>
+        <v>291kidy@2025</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -779,7 +782,7 @@
       </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
-        <v>292 - kidy@2025</v>
+        <v>292kidy@2025</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -788,7 +791,7 @@
       </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
-        <v>294 - kidy@2025</v>
+        <v>294kidy@2025</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -797,7 +800,7 @@
       </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
-        <v>296 - kidy@2025</v>
+        <v>296kidy@2025</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -806,7 +809,7 @@
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
-        <v>297 - kidy@2025</v>
+        <v>297kidy@2025</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -815,7 +818,7 @@
       </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
-        <v>298 - kidy@2025</v>
+        <v>298kidy@2025</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -824,7 +827,7 @@
       </c>
       <c r="B44" t="str">
         <f t="shared" si="0"/>
-        <v>299 - kidy@2025</v>
+        <v>299kidy@2025</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -833,7 +836,7 @@
       </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
-        <v>301 - kidy@2025</v>
+        <v>301kidy@2025</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -842,7 +845,7 @@
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
-        <v>302 - kidy@2025</v>
+        <v>302kidy@2025</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -851,7 +854,7 @@
       </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
-        <v>308 - kidy@2025</v>
+        <v>308kidy@2025</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -860,7 +863,7 @@
       </c>
       <c r="B48" t="str">
         <f t="shared" si="0"/>
-        <v>311 - kidy@2025</v>
+        <v>311kidy@2025</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -869,7 +872,7 @@
       </c>
       <c r="B49" t="str">
         <f t="shared" si="0"/>
-        <v>315 - kidy@2025</v>
+        <v>315kidy@2025</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -878,7 +881,7 @@
       </c>
       <c r="B50" t="str">
         <f t="shared" si="0"/>
-        <v>316 - kidy@2025</v>
+        <v>316kidy@2025</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -887,7 +890,7 @@
       </c>
       <c r="B51" t="str">
         <f t="shared" si="0"/>
-        <v>317 - kidy@2025</v>
+        <v>317kidy@2025</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -896,7 +899,15 @@
       </c>
       <c r="B52" t="str">
         <f t="shared" si="0"/>
-        <v>320 - kidy@2025</v>
+        <v>320kidy@2025</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>2</v>
+      </c>
+      <c r="B53">
+        <v>497980</v>
       </c>
     </row>
   </sheetData>

--- a/auth.xlsx
+++ b/auth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\preditiva\PREDITIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F212AB-D106-42F3-AEFC-FA363EB6E313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBFBB37-BFB5-44E8-A329-C8BEA095FECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6A472DFD-0E09-42DB-874E-9233951C7FB7}"/>
   </bookViews>
@@ -35,20 +35,20 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Usuario</t>
+    <t>admin</t>
   </si>
   <si>
-    <t>Senha</t>
+    <t>usuario</t>
   </si>
   <si>
-    <t>admin</t>
+    <t>senha</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -60,6 +60,13 @@
       <sz val="11"/>
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -111,10 +118,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,14 +444,14 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>11</v>
       </c>
       <c r="B2" t="str">
@@ -453,7 +460,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>15</v>
       </c>
       <c r="B3" t="str">
@@ -462,7 +469,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>19</v>
       </c>
       <c r="B4" t="str">
@@ -471,7 +478,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>23</v>
       </c>
       <c r="B5" t="str">
@@ -480,7 +487,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="A6" s="2">
         <v>31</v>
       </c>
       <c r="B6" t="str">
@@ -489,7 +496,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="A7" s="1">
         <v>34</v>
       </c>
       <c r="B7" t="str">
@@ -498,7 +505,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+      <c r="A8" s="2">
         <v>38</v>
       </c>
       <c r="B8" t="str">
@@ -507,7 +514,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="1">
         <v>39</v>
       </c>
       <c r="B9" t="str">
@@ -516,7 +523,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>41</v>
       </c>
       <c r="B10" t="str">
@@ -525,7 +532,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="A11" s="1">
         <v>45</v>
       </c>
       <c r="B11" t="str">
@@ -534,7 +541,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>46</v>
       </c>
       <c r="B12" t="str">
@@ -543,7 +550,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="1">
         <v>53</v>
       </c>
       <c r="B13" t="str">
@@ -552,7 +559,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>61</v>
       </c>
       <c r="B14" t="str">
@@ -561,7 +568,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="1">
         <v>65</v>
       </c>
       <c r="B15" t="str">
@@ -570,7 +577,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>74</v>
       </c>
       <c r="B16" t="str">
@@ -579,7 +586,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="1">
         <v>93</v>
       </c>
       <c r="B17" t="str">
@@ -588,7 +595,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>143</v>
       </c>
       <c r="B18" t="str">
@@ -597,7 +604,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="1">
         <v>167</v>
       </c>
       <c r="B19" t="str">
@@ -606,7 +613,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>371</v>
       </c>
       <c r="B20" t="str">
@@ -615,7 +622,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="A21" s="1">
         <v>178</v>
       </c>
       <c r="B21" t="str">
@@ -624,7 +631,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>187</v>
       </c>
       <c r="B22" t="str">
@@ -633,7 +640,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="1">
         <v>194</v>
       </c>
       <c r="B23" t="str">
@@ -642,7 +649,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>197</v>
       </c>
       <c r="B24" t="str">
@@ -651,7 +658,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="1">
         <v>208</v>
       </c>
       <c r="B25" t="str">
@@ -660,7 +667,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>217</v>
       </c>
       <c r="B26" t="str">
@@ -669,7 +676,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="1">
         <v>218</v>
       </c>
       <c r="B27" t="str">
@@ -678,7 +685,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>231</v>
       </c>
       <c r="B28" t="str">
@@ -687,7 +694,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="1">
         <v>232</v>
       </c>
       <c r="B29" t="str">
@@ -696,7 +703,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3">
+      <c r="A30" s="2">
         <v>240</v>
       </c>
       <c r="B30" t="str">
@@ -705,7 +712,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="1">
         <v>248</v>
       </c>
       <c r="B31" t="str">
@@ -714,7 +721,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="A32" s="2">
         <v>261</v>
       </c>
       <c r="B32" t="str">
@@ -723,7 +730,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="A33" s="1">
         <v>266</v>
       </c>
       <c r="B33" t="str">
@@ -732,7 +739,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="A34" s="2">
         <v>267</v>
       </c>
       <c r="B34" t="str">
@@ -741,7 +748,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="A35" s="1">
         <v>270</v>
       </c>
       <c r="B35" t="str">
@@ -750,7 +757,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="3">
+      <c r="A36" s="2">
         <v>273</v>
       </c>
       <c r="B36" t="str">
@@ -759,7 +766,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="A37" s="1">
         <v>282</v>
       </c>
       <c r="B37" t="str">
@@ -768,7 +775,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+      <c r="A38" s="2">
         <v>291</v>
       </c>
       <c r="B38" t="str">
@@ -777,7 +784,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="A39" s="1">
         <v>292</v>
       </c>
       <c r="B39" t="str">
@@ -786,7 +793,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="3">
+      <c r="A40" s="2">
         <v>294</v>
       </c>
       <c r="B40" t="str">
@@ -795,7 +802,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="A41" s="1">
         <v>296</v>
       </c>
       <c r="B41" t="str">
@@ -804,7 +811,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="3">
+      <c r="A42" s="2">
         <v>297</v>
       </c>
       <c r="B42" t="str">
@@ -813,7 +820,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="A43" s="1">
         <v>298</v>
       </c>
       <c r="B43" t="str">
@@ -822,7 +829,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3">
+      <c r="A44" s="2">
         <v>299</v>
       </c>
       <c r="B44" t="str">
@@ -831,7 +838,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="A45" s="1">
         <v>301</v>
       </c>
       <c r="B45" t="str">
@@ -840,7 +847,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="3">
+      <c r="A46" s="2">
         <v>302</v>
       </c>
       <c r="B46" t="str">
@@ -849,7 +856,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="A47" s="1">
         <v>308</v>
       </c>
       <c r="B47" t="str">
@@ -858,7 +865,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="3">
+      <c r="A48" s="2">
         <v>311</v>
       </c>
       <c r="B48" t="str">
@@ -867,7 +874,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="A49" s="1">
         <v>315</v>
       </c>
       <c r="B49" t="str">
@@ -876,7 +883,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+      <c r="A50" s="2">
         <v>316</v>
       </c>
       <c r="B50" t="str">
@@ -885,7 +892,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+      <c r="A51" s="3">
         <v>317</v>
       </c>
       <c r="B51" t="str">
@@ -894,7 +901,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+      <c r="A52" s="2">
         <v>320</v>
       </c>
       <c r="B52" t="str">
@@ -904,7 +911,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B53">
         <v>497980</v>
@@ -912,5 +919,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/auth.xlsx
+++ b/auth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\preditiva\PREDITIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBFBB37-BFB5-44E8-A329-C8BEA095FECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500FD112-DB3D-4471-9C5D-3A5B0259A027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6A472DFD-0E09-42DB-874E-9233951C7FB7}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +67,20 @@
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -116,12 +130,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,21 +454,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F37F4D-7674-4A32-8889-363E089154EA}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>11</v>
       </c>
@@ -459,7 +477,7 @@
         <v>11kidy@2025</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>15</v>
       </c>
@@ -468,7 +486,7 @@
         <v>15kidy@2025</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>19</v>
       </c>
@@ -477,7 +495,7 @@
         <v>19kidy@2025</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>23</v>
       </c>
@@ -486,7 +504,7 @@
         <v>23kidy@2025</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>31</v>
       </c>
@@ -495,7 +513,7 @@
         <v>31kidy@2025</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>34</v>
       </c>
@@ -504,7 +522,7 @@
         <v>34kidy@2025</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>38</v>
       </c>
@@ -512,8 +530,9 @@
         <f t="shared" si="0"/>
         <v>38kidy@2025</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>39</v>
       </c>
@@ -522,7 +541,7 @@
         <v>39kidy@2025</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>41</v>
       </c>
@@ -531,7 +550,7 @@
         <v>41kidy@2025</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45</v>
       </c>
@@ -540,7 +559,7 @@
         <v>45kidy@2025</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46</v>
       </c>
@@ -549,7 +568,7 @@
         <v>46kidy@2025</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>53</v>
       </c>
@@ -558,7 +577,7 @@
         <v>53kidy@2025</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>61</v>
       </c>
@@ -567,7 +586,7 @@
         <v>61kidy@2025</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>65</v>
       </c>
@@ -576,7 +595,7 @@
         <v>65kidy@2025</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>74</v>
       </c>

--- a/auth.xlsx
+++ b/auth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\preditiva\PREDITIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500FD112-DB3D-4471-9C5D-3A5B0259A027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45577831-0EBD-4F71-9A25-BF9AB5BD0F48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6A472DFD-0E09-42DB-874E-9233951C7FB7}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="8">
   <si>
     <t>admin</t>
   </si>
@@ -43,13 +43,36 @@
   <si>
     <t>senha</t>
   </si>
+  <si>
+    <t>codigo_supervisor</t>
+  </si>
+  <si>
+    <t>perfil</t>
+  </si>
+  <si>
+    <t>codigo_representante</t>
+  </si>
+  <si>
+    <t>vendas</t>
+  </si>
+  <si>
+    <t>supervisor</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -81,6 +104,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -130,16 +159,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,21 +489,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F37F4D-7674-4A32-8889-363E089154EA}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>11</v>
       </c>
@@ -476,17 +522,35 @@
         <f>A2&amp;"kidy@2025"</f>
         <v>11kidy@2025</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="7">
+        <v>9902</v>
+      </c>
+      <c r="E2" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>15</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B52" si="0">A3&amp;"kidy@2025"</f>
+        <f t="shared" ref="B3:B59" si="0">A3&amp;"kidy@2025"</f>
         <v>15kidy@2025</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E3" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>19</v>
       </c>
@@ -494,8 +558,17 @@
         <f t="shared" si="0"/>
         <v>19kidy@2025</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="9">
+        <v>9917</v>
+      </c>
+      <c r="E4" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>23</v>
       </c>
@@ -503,8 +576,17 @@
         <f t="shared" si="0"/>
         <v>23kidy@2025</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="8">
+        <v>9907</v>
+      </c>
+      <c r="E5" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>31</v>
       </c>
@@ -512,8 +594,17 @@
         <f t="shared" si="0"/>
         <v>31kidy@2025</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="9">
+        <v>9914</v>
+      </c>
+      <c r="E6" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>34</v>
       </c>
@@ -521,8 +612,17 @@
         <f t="shared" si="0"/>
         <v>34kidy@2025</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="8">
+        <v>9915</v>
+      </c>
+      <c r="E7" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>38</v>
       </c>
@@ -530,9 +630,18 @@
         <f t="shared" si="0"/>
         <v>38kidy@2025</v>
       </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="9">
+        <v>9915</v>
+      </c>
+      <c r="E8" s="2">
+        <v>38</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>39</v>
       </c>
@@ -540,8 +649,17 @@
         <f t="shared" si="0"/>
         <v>39kidy@2025</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="8">
+        <v>9916</v>
+      </c>
+      <c r="E9" s="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>41</v>
       </c>
@@ -549,8 +667,17 @@
         <f t="shared" si="0"/>
         <v>41kidy@2025</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="9">
+        <v>9917</v>
+      </c>
+      <c r="E10" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>45</v>
       </c>
@@ -558,8 +685,17 @@
         <f t="shared" si="0"/>
         <v>45kidy@2025</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="8">
+        <v>9907</v>
+      </c>
+      <c r="E11" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46</v>
       </c>
@@ -567,8 +703,17 @@
         <f t="shared" si="0"/>
         <v>46kidy@2025</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="9">
+        <v>9907</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>53</v>
       </c>
@@ -576,8 +721,17 @@
         <f t="shared" si="0"/>
         <v>53kidy@2025</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E13" s="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>61</v>
       </c>
@@ -585,8 +739,17 @@
         <f t="shared" si="0"/>
         <v>61kidy@2025</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="9">
+        <v>9915</v>
+      </c>
+      <c r="E14" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>65</v>
       </c>
@@ -594,8 +757,17 @@
         <f t="shared" si="0"/>
         <v>65kidy@2025</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="8">
+        <v>9902</v>
+      </c>
+      <c r="E15" s="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>74</v>
       </c>
@@ -603,8 +775,17 @@
         <f t="shared" si="0"/>
         <v>74kidy@2025</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="9">
+        <v>9907</v>
+      </c>
+      <c r="E16" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>93</v>
       </c>
@@ -612,8 +793,17 @@
         <f t="shared" si="0"/>
         <v>93kidy@2025</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="8">
+        <v>9907</v>
+      </c>
+      <c r="E17" s="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>143</v>
       </c>
@@ -621,8 +811,17 @@
         <f t="shared" si="0"/>
         <v>143kidy@2025</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="9">
+        <v>9917</v>
+      </c>
+      <c r="E18" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>167</v>
       </c>
@@ -630,8 +829,17 @@
         <f t="shared" si="0"/>
         <v>167kidy@2025</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="8">
+        <v>9915</v>
+      </c>
+      <c r="E19" s="1">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>371</v>
       </c>
@@ -639,8 +847,17 @@
         <f t="shared" si="0"/>
         <v>371kidy@2025</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="9">
+        <v>9915</v>
+      </c>
+      <c r="E20" s="2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>178</v>
       </c>
@@ -648,8 +865,17 @@
         <f t="shared" si="0"/>
         <v>178kidy@2025</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="8">
+        <v>9907</v>
+      </c>
+      <c r="E21" s="1">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>187</v>
       </c>
@@ -657,8 +883,17 @@
         <f t="shared" si="0"/>
         <v>187kidy@2025</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="9">
+        <v>9907</v>
+      </c>
+      <c r="E22" s="2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>194</v>
       </c>
@@ -666,8 +901,17 @@
         <f t="shared" si="0"/>
         <v>194kidy@2025</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E23" s="1">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>197</v>
       </c>
@@ -675,8 +919,17 @@
         <f t="shared" si="0"/>
         <v>197kidy@2025</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="9">
+        <v>9917</v>
+      </c>
+      <c r="E24" s="2">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>208</v>
       </c>
@@ -684,8 +937,17 @@
         <f t="shared" si="0"/>
         <v>208kidy@2025</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E25" s="1">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>217</v>
       </c>
@@ -693,8 +955,17 @@
         <f t="shared" si="0"/>
         <v>217kidy@2025</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="9">
+        <v>9914</v>
+      </c>
+      <c r="E26" s="2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>218</v>
       </c>
@@ -702,8 +973,17 @@
         <f t="shared" si="0"/>
         <v>218kidy@2025</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E27" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>231</v>
       </c>
@@ -711,8 +991,17 @@
         <f t="shared" si="0"/>
         <v>231kidy@2025</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="9">
+        <v>9907</v>
+      </c>
+      <c r="E28" s="2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>232</v>
       </c>
@@ -720,8 +1009,17 @@
         <f t="shared" si="0"/>
         <v>232kidy@2025</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E29" s="1">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>240</v>
       </c>
@@ -729,8 +1027,17 @@
         <f t="shared" si="0"/>
         <v>240kidy@2025</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="9">
+        <v>9914</v>
+      </c>
+      <c r="E30" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>248</v>
       </c>
@@ -738,8 +1045,17 @@
         <f t="shared" si="0"/>
         <v>248kidy@2025</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="8">
+        <v>9907</v>
+      </c>
+      <c r="E31" s="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>261</v>
       </c>
@@ -747,8 +1063,17 @@
         <f t="shared" si="0"/>
         <v>261kidy@2025</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="9">
+        <v>9902</v>
+      </c>
+      <c r="E32" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>266</v>
       </c>
@@ -756,8 +1081,17 @@
         <f t="shared" si="0"/>
         <v>266kidy@2025</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="8">
+        <v>9902</v>
+      </c>
+      <c r="E33" s="1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>267</v>
       </c>
@@ -765,8 +1099,17 @@
         <f t="shared" si="0"/>
         <v>267kidy@2025</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="9">
+        <v>9914</v>
+      </c>
+      <c r="E34" s="2">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>270</v>
       </c>
@@ -774,8 +1117,17 @@
         <f t="shared" si="0"/>
         <v>270kidy@2025</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="8">
+        <v>9915</v>
+      </c>
+      <c r="E35" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>273</v>
       </c>
@@ -783,8 +1135,17 @@
         <f t="shared" si="0"/>
         <v>273kidy@2025</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="9">
+        <v>9914</v>
+      </c>
+      <c r="E36" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>282</v>
       </c>
@@ -792,8 +1153,17 @@
         <f t="shared" si="0"/>
         <v>282kidy@2025</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="8">
+        <v>9916</v>
+      </c>
+      <c r="E37" s="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>291</v>
       </c>
@@ -801,8 +1171,17 @@
         <f t="shared" si="0"/>
         <v>291kidy@2025</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="9">
+        <v>9907</v>
+      </c>
+      <c r="E38" s="2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>292</v>
       </c>
@@ -810,8 +1189,17 @@
         <f t="shared" si="0"/>
         <v>292kidy@2025</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="8">
+        <v>9915</v>
+      </c>
+      <c r="E39" s="1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>294</v>
       </c>
@@ -819,8 +1207,17 @@
         <f t="shared" si="0"/>
         <v>294kidy@2025</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="9">
+        <v>9917</v>
+      </c>
+      <c r="E40" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>296</v>
       </c>
@@ -828,8 +1225,17 @@
         <f t="shared" si="0"/>
         <v>296kidy@2025</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="8">
+        <v>9902</v>
+      </c>
+      <c r="E41" s="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>297</v>
       </c>
@@ -837,8 +1243,17 @@
         <f t="shared" si="0"/>
         <v>297kidy@2025</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="9">
+        <v>9917</v>
+      </c>
+      <c r="E42" s="2">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>298</v>
       </c>
@@ -846,8 +1261,17 @@
         <f t="shared" si="0"/>
         <v>298kidy@2025</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E43" s="1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>299</v>
       </c>
@@ -855,8 +1279,17 @@
         <f t="shared" si="0"/>
         <v>299kidy@2025</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="9">
+        <v>9915</v>
+      </c>
+      <c r="E44" s="2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>301</v>
       </c>
@@ -864,8 +1297,17 @@
         <f t="shared" si="0"/>
         <v>301kidy@2025</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E45" s="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>302</v>
       </c>
@@ -873,8 +1315,17 @@
         <f t="shared" si="0"/>
         <v>302kidy@2025</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="9">
+        <v>9915</v>
+      </c>
+      <c r="E46" s="2">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>308</v>
       </c>
@@ -882,8 +1333,17 @@
         <f t="shared" si="0"/>
         <v>308kidy@2025</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="8">
+        <v>9914</v>
+      </c>
+      <c r="E47" s="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>311</v>
       </c>
@@ -891,8 +1351,17 @@
         <f t="shared" si="0"/>
         <v>311kidy@2025</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="9">
+        <v>9917</v>
+      </c>
+      <c r="E48" s="2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>315</v>
       </c>
@@ -900,8 +1369,17 @@
         <f t="shared" si="0"/>
         <v>315kidy@2025</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="8">
+        <v>9907</v>
+      </c>
+      <c r="E49" s="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>316</v>
       </c>
@@ -909,8 +1387,17 @@
         <f t="shared" si="0"/>
         <v>316kidy@2025</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="9">
+        <v>9902</v>
+      </c>
+      <c r="E50" s="2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>317</v>
       </c>
@@ -918,8 +1405,17 @@
         <f t="shared" si="0"/>
         <v>317kidy@2025</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="8">
+        <v>9902</v>
+      </c>
+      <c r="E51" s="3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>320</v>
       </c>
@@ -927,13 +1423,124 @@
         <f t="shared" si="0"/>
         <v>320kidy@2025</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="9">
+        <v>9915</v>
+      </c>
+      <c r="E52" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>0</v>
       </c>
       <c r="B53">
         <v>497980</v>
+      </c>
+      <c r="C53" t="s">
+        <v>0</v>
+      </c>
+      <c r="E53" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>9902</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="0"/>
+        <v>9902kidy@2025</v>
+      </c>
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54">
+        <f>A54</f>
+        <v>9902</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>9907</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="0"/>
+        <v>9907kidy@2025</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55">
+        <f t="shared" ref="D55:D59" si="1">A55</f>
+        <v>9907</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>9914</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="0"/>
+        <v>9914kidy@2025</v>
+      </c>
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="1"/>
+        <v>9914</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>9915</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" si="0"/>
+        <v>9915kidy@2025</v>
+      </c>
+      <c r="C57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="1"/>
+        <v>9915</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>9916</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="0"/>
+        <v>9916kidy@2025</v>
+      </c>
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="1"/>
+        <v>9916</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>9917</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="0"/>
+        <v>9917kidy@2025</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="1"/>
+        <v>9917</v>
       </c>
     </row>
   </sheetData>
